--- a/data/public_toilet/data.xlsx
+++ b/data/public_toilet/data.xlsx
@@ -648,19 +648,19 @@
         <v>4</v>
       </c>
       <c r="P3" t="str">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q3" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R3" t="str">
         <v>5</v>
       </c>
       <c r="S3" t="str">
-        <v>2</v>
+        <v/>
       </c>
       <c r="T3" t="str">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U3" t="str">
         <v/>
@@ -1456,19 +1456,19 @@
         <v>3</v>
       </c>
       <c r="P11" t="str">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q11" t="str">
-        <v/>
+        <v>1</v>
       </c>
       <c r="R11" t="str">
         <v>2</v>
       </c>
       <c r="S11" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T11" t="str">
-        <v/>
+        <v>1</v>
       </c>
       <c r="U11" t="str">
         <v>1</v>
